--- a/config/组合测控/电表_乔宇电气.xlsx
+++ b/config/组合测控/电表_乔宇电气.xlsx
@@ -161,7 +161,7 @@
     <t>总有功功率</t>
   </si>
   <si>
-    <t>W</t>
+    <t>kW</t>
   </si>
   <si>
     <t>totalActivePower</t>
@@ -200,7 +200,7 @@
     <t>总无功功率</t>
   </si>
   <si>
-    <t>Var</t>
+    <t>kVar</t>
   </si>
   <si>
     <t>totalReactivePower</t>
@@ -239,7 +239,7 @@
     <t>总视在功率</t>
   </si>
   <si>
-    <t>VA</t>
+    <t>kVA</t>
   </si>
   <si>
     <t>totalApparentPower</t>
@@ -1074,7 +1074,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1088,6 +1088,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1828,7 +1831,7 @@
         <v>20</v>
       </c>
       <c r="J5" s="2">
-        <v>0.001</v>
+        <v>0.25</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
@@ -1866,7 +1869,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="2">
-        <v>0.001</v>
+        <v>0.25</v>
       </c>
       <c r="K6" s="2">
         <v>0</v>
@@ -1904,7 +1907,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="2">
-        <v>0.001</v>
+        <v>0.25</v>
       </c>
       <c r="K7" s="2">
         <v>0</v>
@@ -1942,7 +1945,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="2">
-        <v>0.001</v>
+        <v>0.25</v>
       </c>
       <c r="K8" s="2">
         <v>0</v>
@@ -1980,7 +1983,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="2">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K9" s="2">
         <v>0</v>
@@ -2017,8 +2020,8 @@
       <c r="I10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="2">
-        <v>1</v>
+      <c r="J10" s="6">
+        <v>0.25</v>
       </c>
       <c r="K10" s="2">
         <v>0</v>
@@ -2055,8 +2058,8 @@
       <c r="I11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="2">
-        <v>1</v>
+      <c r="J11" s="6">
+        <v>0.25</v>
       </c>
       <c r="K11" s="2">
         <v>0</v>
@@ -2093,8 +2096,8 @@
       <c r="I12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="2">
-        <v>1</v>
+      <c r="J12" s="6">
+        <v>0.25</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
@@ -2131,8 +2134,8 @@
       <c r="I13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J13" s="2">
-        <v>1</v>
+      <c r="J13" s="6">
+        <v>0.25</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -2169,8 +2172,8 @@
       <c r="I14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="2">
-        <v>1</v>
+      <c r="J14" s="6">
+        <v>0.25</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -2186,7 +2189,7 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2207,8 +2210,8 @@
       <c r="I15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="2">
-        <v>1</v>
+      <c r="J15" s="6">
+        <v>0.25</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
@@ -2224,7 +2227,7 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>66</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -2245,8 +2248,8 @@
       <c r="I16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="2">
-        <v>1</v>
+      <c r="J16" s="6">
+        <v>0.25</v>
       </c>
       <c r="K16" s="2">
         <v>0</v>
@@ -2283,8 +2286,8 @@
       <c r="I17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="2">
-        <v>1</v>
+      <c r="J17" s="6">
+        <v>0.25</v>
       </c>
       <c r="K17" s="2">
         <v>0</v>
@@ -2306,7 +2309,7 @@
       <c r="C18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="5" t="s">
         <v>70</v>
       </c>
       <c r="F18" s="2">
@@ -2321,8 +2324,8 @@
       <c r="I18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J18" s="2">
-        <v>1</v>
+      <c r="J18" s="6">
+        <v>0.25</v>
       </c>
       <c r="K18" s="2">
         <v>0</v>
@@ -2338,7 +2341,7 @@
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>76</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -2359,8 +2362,8 @@
       <c r="I19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J19" s="2">
-        <v>1</v>
+      <c r="J19" s="6">
+        <v>0.25</v>
       </c>
       <c r="K19" s="2">
         <v>0</v>
@@ -2376,7 +2379,7 @@
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2397,8 +2400,8 @@
       <c r="I20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="2">
-        <v>1</v>
+      <c r="J20" s="6">
+        <v>0.25</v>
       </c>
       <c r="K20" s="2">
         <v>0</v>
@@ -2630,7 +2633,7 @@
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2668,7 +2671,7 @@
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>103</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2706,7 +2709,7 @@
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2744,7 +2747,7 @@
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>110</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2804,7 +2807,7 @@
         <v>116</v>
       </c>
       <c r="J31" s="2">
-        <v>0.01</v>
+        <v>2.5</v>
       </c>
       <c r="K31" s="2">
         <v>0</v>
@@ -2842,7 +2845,7 @@
         <v>116</v>
       </c>
       <c r="J32" s="2">
-        <v>0.01</v>
+        <v>2.5</v>
       </c>
       <c r="K32" s="2">
         <v>0</v>
@@ -2880,7 +2883,7 @@
         <v>116</v>
       </c>
       <c r="J33" s="2">
-        <v>0.01</v>
+        <v>2.5</v>
       </c>
       <c r="K33" s="2">
         <v>0</v>
@@ -2918,7 +2921,7 @@
         <v>116</v>
       </c>
       <c r="J34" s="2">
-        <v>0.01</v>
+        <v>2.5</v>
       </c>
       <c r="K34" s="2">
         <v>0</v>
